--- a/tests/A01_pixell_test_plan_client.xlsx
+++ b/tests/A01_pixell_test_plan_client.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>#VALUE!</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>Developer:</t>
+  </si>
+  <si>
+    <t>Robinpreet Kaur</t>
   </si>
   <si>
     <t>Class Name:</t>
@@ -833,7 +836,9 @@
       <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9"/>
+      <c r="C3" s="9" t="s">
+        <v>3</v>
+      </c>
       <c r="D3" s="10"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -842,10 +847,10 @@
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
       <c r="A4" s="1"/>
       <c r="B4" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="3"/>
@@ -864,22 +869,22 @@
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1"/>
       <c r="B6" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
@@ -888,19 +893,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="31.5">
@@ -909,19 +914,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="31.5">
@@ -930,19 +935,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>19</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>18</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="66">
@@ -951,19 +956,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="66">
@@ -972,19 +977,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="31.149999999999995">
@@ -993,16 +998,16 @@
         <v>6</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="23">
         <v>2050</v>
@@ -1014,19 +1019,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>28</v>
-      </c>
       <c r="F13" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="31.149999999999995">
@@ -1035,19 +1040,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="31.149999999999995">
@@ -1056,19 +1061,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="31.149999999999995" customFormat="1" s="24">
@@ -1077,19 +1082,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="31.149999999999995">
@@ -1236,7 +1241,7 @@
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="1"/>
       <c r="B30" s="26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
